--- a/Data/kategoriak.xlsx
+++ b/Data/kategoriak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Felina\PythonProjects\FromLoginToNexonImportBonuses\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Aleksei/Dropbox/Projects/Felina/PythonProjects/FromLoginToNexonImportBonuses/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C44FBFF-C463-4315-B302-467A52DD5BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F422355-EC90-3942-A17C-B08E2253ED8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kategoriak" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="16">
   <si>
     <t>kat</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>202402</t>
-  </si>
-  <si>
-    <t>202412</t>
   </si>
   <si>
     <t>BASE</t>
@@ -192,9 +189,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +229,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -338,7 +335,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,7 +477,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -488,10 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H67"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,12 +514,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -536,19 +533,19 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
+      <c r="G2">
+        <v>202412</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -562,19 +559,19 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
+      <c r="G3">
+        <v>202412</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -588,92 +585,92 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
-        <v>15</v>
+      <c r="G4">
+        <v>202412</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
+        <v>266800</v>
+      </c>
+      <c r="F5">
+        <v>202501</v>
+      </c>
+      <c r="G5">
+        <v>202512</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
       <c r="C6">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
+        <v>281175</v>
+      </c>
+      <c r="F6">
+        <v>202501</v>
+      </c>
+      <c r="G6">
+        <v>202512</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
       <c r="C7">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
+        <v>295550</v>
+      </c>
+      <c r="F7">
+        <v>202501</v>
+      </c>
+      <c r="G7">
+        <v>202512</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -681,10 +678,10 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D8">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -692,14 +689,14 @@
       <c r="F8" t="s">
         <v>14</v>
       </c>
-      <c r="G8" t="s">
-        <v>15</v>
+      <c r="G8">
+        <v>202512</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -707,10 +704,10 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -718,14 +715,14 @@
       <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="G9" t="s">
-        <v>15</v>
+      <c r="G9">
+        <v>202512</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -733,10 +730,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D10">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -744,25 +741,25 @@
       <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="G10" t="s">
-        <v>15</v>
+      <c r="G10">
+        <v>202512</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -770,25 +767,25 @@
       <c r="F11" t="s">
         <v>14</v>
       </c>
-      <c r="G11" t="s">
-        <v>15</v>
+      <c r="G11">
+        <v>202512</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D12">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -796,25 +793,25 @@
       <c r="F12" t="s">
         <v>14</v>
       </c>
-      <c r="G12" t="s">
-        <v>15</v>
+      <c r="G12">
+        <v>202512</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D13">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -822,14 +819,14 @@
       <c r="F13" t="s">
         <v>14</v>
       </c>
-      <c r="G13" t="s">
-        <v>15</v>
+      <c r="G13">
+        <v>202512</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -837,10 +834,10 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D14">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -848,14 +845,14 @@
       <c r="F14" t="s">
         <v>14</v>
       </c>
-      <c r="G14" t="s">
-        <v>15</v>
+      <c r="G14">
+        <v>202512</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -863,10 +860,10 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -874,14 +871,14 @@
       <c r="F15" t="s">
         <v>14</v>
       </c>
-      <c r="G15" t="s">
-        <v>15</v>
+      <c r="G15">
+        <v>202512</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -889,10 +886,10 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D16">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -900,25 +897,25 @@
       <c r="F16" t="s">
         <v>14</v>
       </c>
-      <c r="G16" t="s">
-        <v>15</v>
+      <c r="G16">
+        <v>202512</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D17">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -926,25 +923,25 @@
       <c r="F17" t="s">
         <v>14</v>
       </c>
-      <c r="G17" t="s">
-        <v>15</v>
+      <c r="G17">
+        <v>202512</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D18">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -952,25 +949,25 @@
       <c r="F18" t="s">
         <v>14</v>
       </c>
-      <c r="G18" t="s">
-        <v>15</v>
+      <c r="G18">
+        <v>202512</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -978,14 +975,14 @@
       <c r="F19" t="s">
         <v>14</v>
       </c>
-      <c r="G19" t="s">
-        <v>15</v>
+      <c r="G19">
+        <v>202512</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -993,10 +990,10 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D20">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1004,14 +1001,14 @@
       <c r="F20" t="s">
         <v>14</v>
       </c>
-      <c r="G20" t="s">
-        <v>15</v>
+      <c r="G20">
+        <v>202512</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -1019,10 +1016,10 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1030,14 +1027,14 @@
       <c r="F21" t="s">
         <v>14</v>
       </c>
-      <c r="G21" t="s">
-        <v>15</v>
+      <c r="G21">
+        <v>202512</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1045,103 +1042,103 @@
         <v>9</v>
       </c>
       <c r="C22">
+        <v>85</v>
+      </c>
+      <c r="D22">
+        <v>90</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22">
+        <v>202512</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>90</v>
+      </c>
+      <c r="D23">
+        <v>95</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>202512</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>95</v>
+      </c>
+      <c r="D24">
         <v>100</v>
       </c>
-      <c r="D22">
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24">
+        <v>202512</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
         <v>999</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23">
-        <v>75</v>
-      </c>
-      <c r="D23">
-        <v>80</v>
-      </c>
-      <c r="E23">
-        <v>7000</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24">
-        <v>80</v>
-      </c>
-      <c r="D24">
-        <v>85</v>
-      </c>
-      <c r="E24">
-        <v>14000</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25">
-        <v>85</v>
-      </c>
-      <c r="D25">
-        <v>90</v>
-      </c>
       <c r="E25">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
-      <c r="G25" t="s">
-        <v>15</v>
+      <c r="G25">
+        <v>202512</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1149,25 +1146,25 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D26">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E26">
-        <v>44000</v>
+        <v>7000</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
-      <c r="G26" t="s">
-        <v>15</v>
+      <c r="G26">
+        <v>202512</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1175,25 +1172,25 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E27">
-        <v>54000</v>
+        <v>14000</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
-      <c r="G27" t="s">
-        <v>15</v>
+      <c r="G27">
+        <v>202512</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1201,103 +1198,103 @@
         <v>12</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D28">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="E28">
-        <v>68000</v>
+        <v>30000</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
-      <c r="G28" t="s">
-        <v>15</v>
+      <c r="G28">
+        <v>202512</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D29">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E29">
-        <v>7000</v>
+        <v>44000</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
-      <c r="G29" t="s">
-        <v>15</v>
+      <c r="G29">
+        <v>202512</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D30">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E30">
-        <v>14000</v>
+        <v>54000</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
-      <c r="G30" t="s">
-        <v>15</v>
+      <c r="G30">
+        <v>202512</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="E31">
-        <v>30000</v>
+        <v>68000</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
-      <c r="G31" t="s">
-        <v>15</v>
+      <c r="G31">
+        <v>202512</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1305,25 +1302,25 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D32">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E32">
-        <v>44000</v>
+        <v>7000</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
-      <c r="G32" t="s">
-        <v>15</v>
+      <c r="G32">
+        <v>202512</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1331,25 +1328,25 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D33">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E33">
-        <v>54000</v>
+        <v>14000</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
-      <c r="G33" t="s">
-        <v>15</v>
+      <c r="G33">
+        <v>202512</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1357,103 +1354,103 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D34">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="E34">
-        <v>68000</v>
+        <v>30000</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
-      <c r="G34" t="s">
-        <v>15</v>
+      <c r="G34">
+        <v>202512</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D35">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E35">
-        <v>7000</v>
+        <v>44000</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
-      <c r="G35" t="s">
-        <v>15</v>
+      <c r="G35">
+        <v>202512</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D36">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E36">
-        <v>14000</v>
+        <v>54000</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
-      <c r="G36" t="s">
-        <v>15</v>
+      <c r="G36">
+        <v>202512</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D37">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="E37">
-        <v>30000</v>
+        <v>68000</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
-      <c r="G37" t="s">
-        <v>15</v>
+      <c r="G37">
+        <v>202512</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -1461,25 +1458,25 @@
         <v>12</v>
       </c>
       <c r="C38">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D38">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E38">
-        <v>44000</v>
+        <v>7000</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
-      <c r="G38" t="s">
-        <v>15</v>
+      <c r="G38">
+        <v>202512</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -1487,25 +1484,25 @@
         <v>12</v>
       </c>
       <c r="C39">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D39">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E39">
-        <v>54000</v>
+        <v>14000</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
-      <c r="G39" t="s">
-        <v>15</v>
+      <c r="G39">
+        <v>202512</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -1513,103 +1510,103 @@
         <v>12</v>
       </c>
       <c r="C40">
+        <v>85</v>
+      </c>
+      <c r="D40">
+        <v>90</v>
+      </c>
+      <c r="E40">
+        <v>30000</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
+        <v>202512</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41">
+        <v>90</v>
+      </c>
+      <c r="D41">
+        <v>95</v>
+      </c>
+      <c r="E41">
+        <v>44000</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>202512</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>95</v>
+      </c>
+      <c r="D42">
         <v>100</v>
       </c>
-      <c r="D40">
+      <c r="E42">
+        <v>54000</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>202512</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>100</v>
+      </c>
+      <c r="D43">
         <v>999</v>
       </c>
-      <c r="E40">
+      <c r="E43">
         <v>68000</v>
       </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41">
-        <v>75</v>
-      </c>
-      <c r="D41">
-        <v>80</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42">
-        <v>80</v>
-      </c>
-      <c r="D42">
-        <v>85</v>
-      </c>
-      <c r="E42">
-        <v>7000</v>
-      </c>
-      <c r="F42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43">
-        <v>85</v>
-      </c>
-      <c r="D43">
-        <v>90</v>
-      </c>
-      <c r="E43">
-        <v>15000</v>
-      </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
-      <c r="G43" t="s">
-        <v>15</v>
+      <c r="G43">
+        <v>202512</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -1617,25 +1614,25 @@
         <v>13</v>
       </c>
       <c r="C44">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D44">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E44">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
-      <c r="G44" t="s">
-        <v>15</v>
+      <c r="G44">
+        <v>202512</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -1643,25 +1640,25 @@
         <v>13</v>
       </c>
       <c r="C45">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D45">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E45">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
-      <c r="G45" t="s">
-        <v>15</v>
+      <c r="G45">
+        <v>202512</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -1669,103 +1666,103 @@
         <v>13</v>
       </c>
       <c r="C46">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D46">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="E46">
-        <v>34000</v>
+        <v>15000</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
-      <c r="G46" t="s">
-        <v>15</v>
+      <c r="G46">
+        <v>202512</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
       </c>
       <c r="C47">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D47">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
-      <c r="G47" t="s">
-        <v>15</v>
+      <c r="G47">
+        <v>202512</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
       </c>
       <c r="C48">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D48">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E48">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
-      <c r="G48" t="s">
-        <v>15</v>
+      <c r="G48">
+        <v>202512</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="C49">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D49">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="E49">
-        <v>15000</v>
+        <v>34000</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
-      <c r="G49" t="s">
-        <v>15</v>
+      <c r="G49">
+        <v>202512</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -1773,25 +1770,25 @@
         <v>13</v>
       </c>
       <c r="C50">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D50">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E50">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
-      <c r="G50" t="s">
-        <v>15</v>
+      <c r="G50">
+        <v>202512</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -1799,25 +1796,25 @@
         <v>13</v>
       </c>
       <c r="C51">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D51">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E51">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
-      <c r="G51" t="s">
-        <v>15</v>
+      <c r="G51">
+        <v>202512</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -1825,103 +1822,103 @@
         <v>13</v>
       </c>
       <c r="C52">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D52">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="E52">
-        <v>34000</v>
+        <v>15000</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
       </c>
-      <c r="G52" t="s">
-        <v>15</v>
+      <c r="G52">
+        <v>202512</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
       </c>
       <c r="C53">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="D53">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
       </c>
-      <c r="G53" t="s">
-        <v>15</v>
+      <c r="G53">
+        <v>202512</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
       </c>
       <c r="C54">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D54">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E54">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
       </c>
-      <c r="G54" t="s">
-        <v>15</v>
+      <c r="G54">
+        <v>202512</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
       </c>
       <c r="C55">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D55">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="E55">
-        <v>15000</v>
+        <v>34000</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
-      <c r="G55" t="s">
-        <v>15</v>
+      <c r="G55">
+        <v>202512</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -1929,25 +1926,25 @@
         <v>13</v>
       </c>
       <c r="C56">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D56">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E56">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
       </c>
-      <c r="G56" t="s">
-        <v>15</v>
+      <c r="G56">
+        <v>202512</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -1955,25 +1952,25 @@
         <v>13</v>
       </c>
       <c r="C57">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D57">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E57">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
-      <c r="G57" t="s">
-        <v>15</v>
+      <c r="G57">
+        <v>202512</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -1981,108 +1978,108 @@
         <v>13</v>
       </c>
       <c r="C58">
+        <v>85</v>
+      </c>
+      <c r="D58">
+        <v>90</v>
+      </c>
+      <c r="E58">
+        <v>15000</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58">
+        <v>202512</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59">
+        <v>90</v>
+      </c>
+      <c r="D59">
+        <v>95</v>
+      </c>
+      <c r="E59">
+        <v>22000</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59">
+        <v>202512</v>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>95</v>
+      </c>
+      <c r="D60">
         <v>100</v>
       </c>
-      <c r="D58">
-        <v>999</v>
-      </c>
-      <c r="E58">
-        <v>34000</v>
-      </c>
-      <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" t="s">
-        <v>15</v>
-      </c>
-      <c r="H58" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>8</v>
-      </c>
-      <c r="B59" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>75</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>75</v>
-      </c>
       <c r="E60">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
-      <c r="G60" t="s">
-        <v>15</v>
+      <c r="G60">
+        <v>202512</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D61">
-        <v>75</v>
+        <v>999</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
-      <c r="G61" t="s">
-        <v>15</v>
+      <c r="G61">
+        <v>202512</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2091,24 +2088,24 @@
         <v>75</v>
       </c>
       <c r="E62">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
       </c>
-      <c r="G62" t="s">
-        <v>15</v>
+      <c r="G62">
+        <v>202512</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2117,24 +2114,24 @@
         <v>75</v>
       </c>
       <c r="E63">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
       </c>
-      <c r="G63" t="s">
-        <v>15</v>
+      <c r="G63">
+        <v>202512</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2143,24 +2140,24 @@
         <v>75</v>
       </c>
       <c r="E64">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
       </c>
-      <c r="G64" t="s">
-        <v>15</v>
+      <c r="G64">
+        <v>202512</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2169,24 +2166,24 @@
         <v>75</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
       </c>
-      <c r="G65" t="s">
-        <v>15</v>
+      <c r="G65">
+        <v>202512</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2195,24 +2192,24 @@
         <v>75</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
       </c>
-      <c r="G66" t="s">
-        <v>15</v>
+      <c r="G66">
+        <v>202512</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2221,15 +2218,93 @@
         <v>75</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
       </c>
-      <c r="G67" t="s">
-        <v>15</v>
+      <c r="G67">
+        <v>202512</v>
       </c>
       <c r="H67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>75</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68">
+        <v>202512</v>
+      </c>
+      <c r="H68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>75</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69">
+        <v>202512</v>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>75</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70">
+        <v>202512</v>
+      </c>
+      <c r="H70" t="b">
         <v>1</v>
       </c>
     </row>
